--- a/Web/TestCases/Facturacion.xlsx
+++ b/Web/TestCases/Facturacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC0AB650-16DB-42C1-A8E7-E8623F7091F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA4D029-17F1-4D65-810B-2C7C3CAD3A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>Num</t>
   </si>
@@ -46,29 +46,40 @@
     <t>Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">1. 
+    <t>pte</t>
+  </si>
+  <si>
+    <t>Invoice page home</t>
+  </si>
+  <si>
+    <t>INV001</t>
+  </si>
+  <si>
+    <t>INV002</t>
+  </si>
+  <si>
+    <t>INV003</t>
+  </si>
+  <si>
+    <t>INV004</t>
+  </si>
+  <si>
+    <t>1. Invoice page home is correctly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks "Facturación"
 </t>
   </si>
   <si>
-    <t>pte</t>
-  </si>
-  <si>
-    <t>Invoice page home</t>
-  </si>
-  <si>
-    <t>INV001</t>
-  </si>
-  <si>
-    <t>INV002</t>
-  </si>
-  <si>
-    <t>INV003</t>
-  </si>
-  <si>
-    <t>INV004</t>
-  </si>
-  <si>
-    <t>1. Invoice page home is correctly.</t>
+    <t>See invoice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects a invoice.
+2. The user sees the invoice.
+</t>
+  </si>
+  <si>
+    <t>1. The invoice is correctly.</t>
   </si>
 </sst>
 </file>
@@ -553,36 +564,42 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="F3" s="3"/>
       <c r="G3" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H3" s="6"/>
     </row>
@@ -591,14 +608,14 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H4" s="4"/>
     </row>
@@ -607,14 +624,14 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H5" s="4"/>
     </row>
